--- a/frontend/public/templates/MERCON_Vehicles_Import_Template.xlsx
+++ b/frontend/public/templates/MERCON_Vehicles_Import_Template.xlsx
@@ -766,8 +766,8 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -788,8 +788,8 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>TELEMATICS INTEGRATION
-Enter ICCES Device ID for Auto GPS Live Tracking</t>
+          <t>TELEMATICS &amp; DRIVER ASSIGNMENT
+Enter ICCES Device ID &amp; Assigned Driver Phone / Name</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
+          <t>Assigned Driver Phone / Name</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
           <t>Trailer Number</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>Trailer Type</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
@@ -876,12 +876,12 @@
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
+          <t>+966 50 123 4567 (Ahmed)</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
           <t>TRL-402</t>
-        </is>
-      </c>
-      <c r="H8" s="9" t="inlineStr">
-        <is>
-          <t>Flatbed</t>
         </is>
       </c>
       <c r="I8" s="11" t="n">
@@ -917,12 +917,12 @@
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
+          <t>+966 50 987 6543 (Tariq)</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
           <t>TRL-405</t>
-        </is>
-      </c>
-      <c r="H9" s="12" t="inlineStr">
-        <is>
-          <t>Reefer</t>
         </is>
       </c>
       <c r="I9" s="14" t="n">
@@ -958,12 +958,12 @@
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
+          <t>+1 555 019 2834 (John)</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
           <t>TRL-409</t>
-        </is>
-      </c>
-      <c r="H10" s="9" t="inlineStr">
-        <is>
-          <t>Tanker</t>
         </is>
       </c>
       <c r="I10" s="11" t="n">
@@ -1528,7 +1528,7 @@
     <mergeCell ref="G4:I5"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="C8:C60 H8:H60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Asset Type" error="Please pick a valid Asset Type from the list" type="list">
+    <dataValidation sqref="C8:C60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Asset Type" error="Please pick a valid Asset Type from the list" type="list">
       <formula1>"Flatbed,Reefer,Box,Tanker"</formula1>
     </dataValidation>
   </dataValidations>
